--- a/RaidenDemo/文档/配置表/StageResource.xlsx
+++ b/RaidenDemo/文档/配置表/StageResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7a5990a5ce294732"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf7209e2793b0487d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -99,7 +99,7 @@
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="200" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="24">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -228,8 +228,22 @@
       <x:color theme="1"/>
       <x:name val="Calibri"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFBDD7EE"/>
+      <x:name val="微软雅黑"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="微软雅黑"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="微软雅黑"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="36">
+  <x:fills count="40">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -406,8 +420,28 @@
         <x:fgColor theme="9" tint="0.39998"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF000000"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3F3F3F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF000000"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF3F3F3F"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="10">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -488,6 +522,20 @@
         <x:color theme="4"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD0D0D0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD0D0D0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD0D0D0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD0D0D0"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="50">
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -639,7 +687,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -657,6 +705,65 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="24" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="37" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="37" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="37" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="38" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="38" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
     <x:cellStyle name="常规" xfId="0"/>
@@ -1092,247 +1199,326 @@
     <x:col min="3" max="3" width="19" customWidth="1"/>
     <x:col min="4" max="4" width="38.75" customWidth="1"/>
     <x:col min="5" max="6" width="18" customWidth="1"/>
-    <x:col min="7" max="8" width="19" customWidth="1"/>
+    <x:col min="7" max="7" width="11.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="9.880000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="1" t="s">
+      <x:c r="A1" s="21" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="21" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="C1" s="21" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="D1" s="21" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="E1" s="21" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="F1" s="21" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="G1" s="21" t="str">
+        <x:v>bossWaveId</x:v>
+      </x:c>
+      <x:c r="H1" s="29" t="str">
+        <x:v>sceneId</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="2" t="s">
+      <x:c r="A2" s="22" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B2" s="2" t="s">
+      <x:c r="B2" s="22" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C2" s="2" t="s">
+      <x:c r="C2" s="22" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D2" s="2" t="s">
+      <x:c r="D2" s="22" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E2" s="2" t="s">
+      <x:c r="E2" s="22" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F2" s="2" t="s">
+      <x:c r="F2" s="22" t="s">
         <x:v>11</x:v>
       </x:c>
+      <x:c r="G2" s="22" t="str">
+        <x:v>Boss波次ID</x:v>
+      </x:c>
+      <x:c r="H2" s="31" t="str">
+        <x:v>场景背景ID</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="1" t="s">
+      <x:c r="A3" s="21" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="B3" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="C3" s="21" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="D3" s="21" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
+      <x:c r="E3" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="F3" s="1" t="s">
+      <x:c r="F3" s="21" t="s">
         <x:v>13</x:v>
       </x:c>
+      <x:c r="G3" s="21" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="H3" s="29" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
-      <x:c r="A4" s="3"/>
-      <x:c r="B4" s="4">
+      <x:c r="A4" s="23"/>
+      <x:c r="B4" s="24">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>101,102,103,104,101,102,103,104</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="n">
+        <x:v>101,102,103,104</x:v>
+      </x:c>
+      <x:c r="E4" s="24" t="n">
         <x:v>402</x:v>
       </x:c>
-      <x:c r="F4" s="4" t="n">
+      <x:c r="F4" s="24" t="n">
         <x:v>1002</x:v>
       </x:c>
+      <x:c r="G4" s="27" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H4" s="27" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="3"/>
-      <x:c r="B5" s="4">
+      <x:c r="A5" s="23"/>
+      <x:c r="B5" s="24">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>201,202,203,201,202,203</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="n">
+        <x:v>201,202,203</x:v>
+      </x:c>
+      <x:c r="E5" s="24" t="n">
         <x:v>602</x:v>
       </x:c>
-      <x:c r="F5" s="4" t="n">
+      <x:c r="F5" s="24" t="n">
         <x:v>1402</x:v>
       </x:c>
+      <x:c r="G5" s="27" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H5" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="4">
+      <x:c r="A6" s="23"/>
+      <x:c r="B6" s="24">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>301,302,303,304,301,302,303,304</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="n">
+        <x:v>301,302,303,304</x:v>
+      </x:c>
+      <x:c r="E6" s="24" t="n">
         <x:v>802</x:v>
       </x:c>
-      <x:c r="F6" s="4" t="n">
+      <x:c r="F6" s="24" t="n">
         <x:v>1602</x:v>
       </x:c>
+      <x:c r="G6" s="27" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H6" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="3"/>
-      <x:c r="B7" s="4">
+      <x:c r="A7" s="23"/>
+      <x:c r="B7" s="24">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>401,402,403,404,401,402,403,404</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="n">
+        <x:v>401,402,403,404</x:v>
+      </x:c>
+      <x:c r="E7" s="24" t="n">
         <x:v>1002</x:v>
       </x:c>
-      <x:c r="F7" s="4" t="n">
+      <x:c r="F7" s="24" t="n">
         <x:v>1802</x:v>
       </x:c>
+      <x:c r="G7" s="27" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H7" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
-      <x:c r="A8" s="3"/>
-      <x:c r="B8" s="4">
+      <x:c r="A8" s="23"/>
+      <x:c r="B8" s="24">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>501,502,503,504,505,501,502,503,504,505</x:v>
-      </x:c>
-      <x:c r="E8" s="4" t="n">
+        <x:v>501,502,503,504,505</x:v>
+      </x:c>
+      <x:c r="E8" s="24" t="n">
         <x:v>1202</x:v>
       </x:c>
-      <x:c r="F8" s="4" t="n">
+      <x:c r="F8" s="24" t="n">
         <x:v>2002</x:v>
       </x:c>
+      <x:c r="G8" s="27" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H8" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
-      <x:c r="A9" s="3"/>
-      <x:c r="B9" s="4">
+      <x:c r="A9" s="23"/>
+      <x:c r="B9" s="24">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>601,602,603,604,605,601,602,603,604,605</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="n">
+        <x:v>601,602,603,604,605</x:v>
+      </x:c>
+      <x:c r="E9" s="24" t="n">
         <x:v>1402</x:v>
       </x:c>
-      <x:c r="F9" s="4" t="n">
+      <x:c r="F9" s="24" t="n">
         <x:v>2402</x:v>
       </x:c>
+      <x:c r="G9" s="27" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H9" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="3"/>
-      <x:c r="B10" s="4">
+      <x:c r="A10" s="23"/>
+      <x:c r="B10" s="24">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>701,702,703,704,705,706,701,702,703,704,705,706</x:v>
-      </x:c>
-      <x:c r="E10" s="4" t="n">
+        <x:v>701,702,703,704,705,706</x:v>
+      </x:c>
+      <x:c r="E10" s="24" t="n">
         <x:v>1602</x:v>
       </x:c>
-      <x:c r="F10" s="4" t="n">
+      <x:c r="F10" s="24" t="n">
         <x:v>2802</x:v>
       </x:c>
+      <x:c r="G10" s="27" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H10" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
-      <x:c r="A11" s="3"/>
-      <x:c r="B11" s="4">
+      <x:c r="A11" s="23"/>
+      <x:c r="B11" s="24">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="5" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>801,802,803,804,805,806,801,802,803,804,805,806</x:v>
-      </x:c>
-      <x:c r="E11" s="4" t="n">
+        <x:v>801,802,803,804,805,806</x:v>
+      </x:c>
+      <x:c r="E11" s="24" t="n">
         <x:v>1802</x:v>
       </x:c>
-      <x:c r="F11" s="4" t="n">
+      <x:c r="F11" s="24" t="n">
         <x:v>3202</x:v>
       </x:c>
+      <x:c r="G11" s="27" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H11" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="3"/>
-      <x:c r="B12" s="4">
+      <x:c r="A12" s="23"/>
+      <x:c r="B12" s="24">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="5" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D12" s="5" t="str">
-        <x:v>901,902,903,904,905,906,907,901,902,903,904,905,906,907</x:v>
-      </x:c>
-      <x:c r="E12" s="4" t="n">
+        <x:v>901,902,903,904,905,906,907</x:v>
+      </x:c>
+      <x:c r="E12" s="24" t="n">
         <x:v>2002</x:v>
       </x:c>
-      <x:c r="F12" s="4" t="n">
+      <x:c r="F12" s="24" t="n">
         <x:v>3602</x:v>
       </x:c>
+      <x:c r="G12" s="27" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H12" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="3"/>
-      <x:c r="B13" s="4">
+      <x:c r="A13" s="23"/>
+      <x:c r="B13" s="24">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="5" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>1001,1002,1003,1004,1005,1006,1007,1001,1002,1003,1004,1005,1006,1007</x:v>
-      </x:c>
-      <x:c r="E13" s="4" t="n">
+        <x:v>1001,1002,1003,1004,1005,1006,1007</x:v>
+      </x:c>
+      <x:c r="E13" s="24" t="n">
         <x:v>2402</x:v>
       </x:c>
-      <x:c r="F13" s="4" t="n">
+      <x:c r="F13" s="24" t="n">
         <x:v>4002</x:v>
+      </x:c>
+      <x:c r="G13" s="27" t="n">
+        <x:v>1101</x:v>
+      </x:c>
+      <x:c r="H13" s="27" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14">

--- a/RaidenDemo/文档/配置表/StageResource.xlsx
+++ b/RaidenDemo/文档/配置表/StageResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf7209e2793b0487d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c1f0e0fd82f4631"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1290,7 +1290,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>101,102,103,104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E4" s="24" t="n">
         <x:v>402</x:v>
@@ -1302,7 +1302,7 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="H4" s="27" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">

--- a/RaidenDemo/文档/配置表/StageResource.xlsx
+++ b/RaidenDemo/文档/配置表/StageResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5c1f0e0fd82f4631"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rca010be54af74266"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1290,7 +1290,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>105</x:v>
+        <x:v>101,102,103,104</x:v>
       </x:c>
       <x:c r="E4" s="24" t="n">
         <x:v>402</x:v>

--- a/RaidenDemo/文档/配置表/StageResource.xlsx
+++ b/RaidenDemo/文档/配置表/StageResource.xlsx
@@ -687,7 +687,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -762,6 +762,9 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="25" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1201,6 +1204,11 @@
     <x:col min="5" max="6" width="18" customWidth="1"/>
     <x:col min="7" max="7" width="11.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="9.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" customWidth="1"/>
+    <x:col min="10" max="10" width="18" customWidth="1"/>
+    <x:col min="11" max="11" width="18" customWidth="1"/>
+    <x:col min="12" max="12" width="18" customWidth="1"/>
+    <x:col min="13" max="13" width="18" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
@@ -1228,6 +1236,31 @@
       <x:c r="H1" s="29" t="str">
         <x:v>sceneId</x:v>
       </x:c>
+      <x:c r="I1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>supplyFirstDelayMs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>supplyIntervalMs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>supplyItemIds</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>waveIntervalMs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M1" s="21" t="inlineStr">
+        <x:is>
+          <x:t>victoryDelayMs</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="22" t="s">
@@ -1254,6 +1287,31 @@
       <x:c r="H2" s="31" t="str">
         <x:v>场景背景ID</x:v>
       </x:c>
+      <x:c r="I2" s="22" t="inlineStr">
+        <x:is>
+          <x:t>补给首次延迟毫秒</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J2" s="22" t="inlineStr">
+        <x:is>
+          <x:t>补给间隔毫秒</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K2" s="22" t="inlineStr">
+        <x:is>
+          <x:t>补给道具顺序</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L2" s="22" t="inlineStr">
+        <x:is>
+          <x:t>编队间隔毫秒</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M2" s="22" t="inlineStr">
+        <x:is>
+          <x:t>胜利结算等待毫秒</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="21" t="s">
@@ -1279,6 +1337,31 @@
       </x:c>
       <x:c r="H3" s="29" t="str">
         <x:v>int</x:v>
+      </x:c>
+      <x:c r="I3" s="21" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J3" s="21" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K3" s="21" t="inlineStr">
+        <x:is>
+          <x:t>(list#sep=,),int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L3" s="21" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M3" s="21" t="inlineStr">
+        <x:is>
+          <x:t>int</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
@@ -1304,6 +1387,23 @@
       <x:c r="H4" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I4" s="27">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J4" s="27">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K4" s="32" t="inlineStr">
+        <x:is>
+          <x:t>1,2,3,4,5,6,7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L4" s="27">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="M4" s="27">
+        <x:v>3500</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="23"/>
@@ -1328,6 +1428,23 @@
       <x:c r="H5" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I5" s="27">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J5" s="27">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K5" s="32" t="inlineStr">
+        <x:is>
+          <x:t>1,2,3,4,5,6,7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L5" s="27">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="M5" s="27">
+        <x:v>3500</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="23"/>
@@ -1352,6 +1469,23 @@
       <x:c r="H6" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I6" s="27">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J6" s="27">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K6" s="32" t="inlineStr">
+        <x:is>
+          <x:t>1,2,3,4,5,6,7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L6" s="27">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="M6" s="27">
+        <x:v>3500</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="23"/>
@@ -1376,6 +1510,23 @@
       <x:c r="H7" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I7" s="27">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J7" s="27">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K7" s="32" t="inlineStr">
+        <x:is>
+          <x:t>1,2,3,4,5,6,7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L7" s="27">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="M7" s="27">
+        <x:v>3500</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" s="23"/>
@@ -1400,6 +1551,23 @@
       <x:c r="H8" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I8" s="27">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J8" s="27">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="inlineStr">
+        <x:is>
+          <x:t>1,2,3,4,5,6,7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L8" s="27">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="M8" s="27">
+        <x:v>3500</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="23"/>
@@ -1424,6 +1592,23 @@
       <x:c r="H9" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I9" s="27">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J9" s="27">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K9" s="32" t="inlineStr">
+        <x:is>
+          <x:t>1,2,3,4,5,6,7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L9" s="27">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="M9" s="27">
+        <x:v>3500</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="23"/>
@@ -1448,6 +1633,23 @@
       <x:c r="H10" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I10" s="27">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J10" s="27">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K10" s="32" t="inlineStr">
+        <x:is>
+          <x:t>1,2,3,4,5,6,7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L10" s="27">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="M10" s="27">
+        <x:v>3500</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="23"/>
@@ -1472,6 +1674,23 @@
       <x:c r="H11" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I11" s="27">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J11" s="27">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K11" s="32" t="inlineStr">
+        <x:is>
+          <x:t>1,2,3,4,5,6,7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L11" s="27">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="M11" s="27">
+        <x:v>3500</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="23"/>
@@ -1496,6 +1715,23 @@
       <x:c r="H12" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I12" s="27">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J12" s="27">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K12" s="32" t="inlineStr">
+        <x:is>
+          <x:t>1,2,3,4,5,6,7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L12" s="27">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="M12" s="27">
+        <x:v>3500</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" s="23"/>
@@ -1520,6 +1756,23 @@
       <x:c r="H13" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="I13" s="27">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J13" s="27">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="K13" s="32" t="inlineStr">
+        <x:is>
+          <x:t>1,2,3,4,5,6,7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L13" s="27">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="M13" s="27">
+        <x:v>3500</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="C14" s="6"/>
